--- a/Employee_Reports_wi52/Mohamed Farkan Mohamed Sareek Q0011.xlsx
+++ b/Employee_Reports_wi52/Mohamed Farkan Mohamed Sareek Q0011.xlsx
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-387</v>
+        <v>-395</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -585,20 +585,20 @@
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>05-Oct-2025</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>05-Oct-2027</t>
+          <t>24-Aug-2028</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>411</v>
+        <v>727</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -631,11 +631,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
